--- a/PhantomBOM.xlsx
+++ b/PhantomBOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7bd69513486a8436/Documents/Phantom/Phantom/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="33" documentId="8_{C253D126-2466-4473-A8D9-932367B4E877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{593C32C3-5C37-454E-A1DF-D87FBF53A834}"/>
+  <xr:revisionPtr revIDLastSave="84" documentId="8_{C253D126-2466-4473-A8D9-932367B4E877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB534472-573D-40F1-AF9C-C8B0C4811D4B}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
   <si>
     <t>Item Name</t>
   </si>
@@ -77,6 +77,114 @@
   </si>
   <si>
     <t>https://www.digikey.com/en/products/detail/tdk/B57330V2103J260/4360622</t>
+  </si>
+  <si>
+    <t>B57330V2103J260</t>
+  </si>
+  <si>
+    <t>PCB Designator</t>
+  </si>
+  <si>
+    <t>U1</t>
+  </si>
+  <si>
+    <t>J1</t>
+  </si>
+  <si>
+    <t>U2</t>
+  </si>
+  <si>
+    <t>U7</t>
+  </si>
+  <si>
+    <t>TH1</t>
+  </si>
+  <si>
+    <t>MCR-B-S-RA-SMT-EH4B-T/R</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/adam-tech/MCR-B-S-RA-SMT-EH4B-T-R/9832095</t>
+  </si>
+  <si>
+    <t>USB</t>
+  </si>
+  <si>
+    <t>J2</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/diodes-incorporated/D3V3XA4B10LP-7/10295141?s=N4IgTCBcDaICIGYBqCAaBBALAIQIwAYAZABRAF0BfIA</t>
+  </si>
+  <si>
+    <t>EMI Protection</t>
+  </si>
+  <si>
+    <t>U3</t>
+  </si>
+  <si>
+    <t>D3V3XA4B10LP-7</t>
+  </si>
+  <si>
+    <t>TLV76733DRVR</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/texas-instruments/TLV76733DRVR/10434657?s=N4IgTCBcDaICoBkBqB2AbCgzJgIgJSTxAF0BfIA</t>
+  </si>
+  <si>
+    <t>Linear Voltage Regulator</t>
+  </si>
+  <si>
+    <t>U5</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/microchip-technology/MCP73871-2CCI-ML/1680971?s=N4IgTCBcDaILIGEAKB2AzADhQRgLRgQRAF0BfIA</t>
+  </si>
+  <si>
+    <t>Battery Charging</t>
+  </si>
+  <si>
+    <t>MCP73871-2CCI/ML</t>
+  </si>
+  <si>
+    <t>U6</t>
+  </si>
+  <si>
+    <t>Display</t>
+  </si>
+  <si>
+    <t>B3U-1100P</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/omron-electronics-inc-emc-div/B3U-1100P/1534339?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20234014242&amp;gbraid=0AAAAADrbLlis3Cz40t9hjOioxPaFcy7Si&amp;gclid=Cj0KCQjw9ZLSBhCcARIsAEhGKgMMIXBGDglw2WMnyUzLqVsnmpcDYfhjn9ClIkeviY8wOCGYYd3g9hoaAp_GEALw_wcB</t>
+  </si>
+  <si>
+    <t>Push Button</t>
+  </si>
+  <si>
+    <t>SW1,SW2</t>
+  </si>
+  <si>
+    <t>U.FL-R-SMT-1(80)</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/hirose-electric-co-ltd/U-FL-R-SMT-1-80/12143318</t>
+  </si>
+  <si>
+    <t>Antenna Connector</t>
+  </si>
+  <si>
+    <t>J4</t>
+  </si>
+  <si>
+    <t>BC501SM</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/mpd-memory-protection-devices/BC501SM/2439260</t>
+  </si>
+  <si>
+    <t>BT1</t>
+  </si>
+  <si>
+    <t>Coin battery holder</t>
   </si>
 </sst>
 </file>
@@ -86,7 +194,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -125,6 +233,12 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -153,7 +267,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -162,6 +276,7 @@
     <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -178,6 +293,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -391,7 +510,7 @@
     <col min="5" max="5" width="38.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -407,8 +526,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>15</v>
       </c>
@@ -424,8 +546,11 @@
       <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F2" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -441,8 +566,11 @@
       <c r="E3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -458,12 +586,31 @@
       <c r="E4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C5" s="2"/>
-      <c r="D5" s="7"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>26</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="2">
+        <v>0.65</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="E5" t="s">
+        <v>28</v>
+      </c>
+      <c r="F5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>13</v>
       </c>
@@ -476,41 +623,160 @@
       <c r="D6" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C7" s="2"/>
+      <c r="E6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7" s="2">
+        <v>0.19</v>
+      </c>
       <c r="D7" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E7" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C8" s="2"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C9" s="2"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C10" s="2"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C11" s="2"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C12" s="2"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="C13" s="2"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F7" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8" s="2">
+        <v>0.44</v>
+      </c>
+      <c r="D8" t="s">
+        <v>30</v>
+      </c>
+      <c r="E8" t="s">
+        <v>31</v>
+      </c>
+      <c r="F8" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="1">
+        <v>1</v>
+      </c>
+      <c r="C9" s="2">
+        <v>1.05</v>
+      </c>
+      <c r="D9" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+      <c r="C10" s="2">
+        <v>2.41</v>
+      </c>
+      <c r="D10" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" t="s">
+        <v>39</v>
+      </c>
+      <c r="F10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B11">
+        <v>2</v>
+      </c>
+      <c r="C11" s="2">
+        <v>1.17</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="E11" t="s">
+        <v>45</v>
+      </c>
+      <c r="F11" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="2">
+        <v>1.27</v>
+      </c>
+      <c r="D12" t="s">
+        <v>48</v>
+      </c>
+      <c r="E12" t="s">
+        <v>49</v>
+      </c>
+      <c r="F12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>51</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1.37</v>
+      </c>
+      <c r="D13" t="s">
+        <v>52</v>
+      </c>
+      <c r="E13" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C14" s="2"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C15" s="2"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C16" s="2"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
@@ -3481,6 +3747,8 @@
     <hyperlink ref="D4" r:id="rId3" xr:uid="{20921124-21F8-4E45-9B63-7C0AAD4C3A92}"/>
     <hyperlink ref="D6" r:id="rId4" xr:uid="{669B1C9F-3CB2-4873-9F39-45EC1B75A88F}"/>
     <hyperlink ref="D7" r:id="rId5" xr:uid="{C3C00219-F6A4-49A2-ACE4-A106BF51F8FC}"/>
+    <hyperlink ref="D9" r:id="rId6" xr:uid="{BB613A42-BF29-46C8-907A-BEAAC1535931}"/>
+    <hyperlink ref="D11" r:id="rId7" display="https://www.digikey.com/en/products/detail/omron-electronics-inc-emc-div/B3U-1100P/1534339?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20234014242&amp;gbraid=0AAAAADrbLlis3Cz40t9hjOioxPaFcy7Si&amp;gclid=Cj0KCQjw9ZLSBhCcARIsAEhGKgMMIXBGDglw2WMnyUzLqVsnmpcDYfhjn9ClIkeviY8wOCGYYd3g9hoaAp_GEALw_wcB" xr:uid="{11DBBCC3-C1AB-458D-A13D-AB15568895F1}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PhantomBOM.xlsx
+++ b/PhantomBOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7bd69513486a8436/Documents/Phantom/Phantom/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="8_{C253D126-2466-4473-A8D9-932367B4E877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BB534472-573D-40F1-AF9C-C8B0C4811D4B}"/>
+  <xr:revisionPtr revIDLastSave="135" documentId="8_{C253D126-2466-4473-A8D9-932367B4E877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E9820A6-E2B7-485A-8FDD-BB43185EF14A}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="75">
   <si>
     <t>Item Name</t>
   </si>
@@ -100,12 +100,6 @@
     <t>TH1</t>
   </si>
   <si>
-    <t>MCR-B-S-RA-SMT-EH4B-T/R</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/adam-tech/MCR-B-S-RA-SMT-EH4B-T-R/9832095</t>
-  </si>
-  <si>
     <t>USB</t>
   </si>
   <si>
@@ -185,6 +179,72 @@
   </si>
   <si>
     <t>Coin battery holder</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/sparkfun-electronics/15141/10130910</t>
+  </si>
+  <si>
+    <t>Rotary Encoder</t>
+  </si>
+  <si>
+    <t>SW3</t>
+  </si>
+  <si>
+    <t>L101011MS02Q</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/c-k/L101011MS02Q/484142</t>
+  </si>
+  <si>
+    <t>Power Switch</t>
+  </si>
+  <si>
+    <t>SW4</t>
+  </si>
+  <si>
+    <t>DX4R005HJ5R2000</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/jae-electronics/DX4R005HJ5R2000/3903227</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/hirose-electric-co-ltd/FH33-10S-0-5SH-10/1305324</t>
+  </si>
+  <si>
+    <t>Screen Connector</t>
+  </si>
+  <si>
+    <t>FH33-10S-0.5SH(10)</t>
+  </si>
+  <si>
+    <t>AGGP.25F.07.0060A</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/taoglas-limited/aggp-25f-07-0060a/3083243</t>
+  </si>
+  <si>
+    <t>GPS Antenna</t>
+  </si>
+  <si>
+    <t>U.FL-R-SMT-K(895)</t>
+  </si>
+  <si>
+    <t>GPS Antenna Connector</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/hirose-electric-co-ltd/U-FL-R-SMT-1-10/2391570</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/models/926641?tab=snapmagic</t>
+  </si>
+  <si>
+    <t>Battery Connector</t>
+  </si>
+  <si>
+    <t>J3</t>
+  </si>
+  <si>
+    <t>B2B-PH-SM4-TB</t>
   </si>
 </sst>
 </file>
@@ -592,22 +652,22 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>26</v>
+        <v>60</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" s="2">
-        <v>0.65</v>
+        <v>0.8</v>
       </c>
       <c r="D5" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="E5" t="s">
+        <v>26</v>
+      </c>
+      <c r="F5" t="s">
         <v>27</v>
-      </c>
-      <c r="E5" t="s">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
@@ -624,7 +684,7 @@
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F6" t="s">
         <v>24</v>
@@ -652,7 +712,7 @@
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B8">
         <v>1</v>
@@ -661,18 +721,18 @@
         <v>0.44</v>
       </c>
       <c r="D8" t="s">
+        <v>28</v>
+      </c>
+      <c r="E8" t="s">
+        <v>29</v>
+      </c>
+      <c r="F8" t="s">
         <v>30</v>
-      </c>
-      <c r="E8" t="s">
-        <v>31</v>
-      </c>
-      <c r="F8" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B9" s="1">
         <v>1</v>
@@ -681,18 +741,18 @@
         <v>1.05</v>
       </c>
       <c r="D9" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>35</v>
-      </c>
-      <c r="E9" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B10">
         <v>1</v>
@@ -700,19 +760,19 @@
       <c r="C10" s="2">
         <v>2.41</v>
       </c>
-      <c r="D10" t="s">
-        <v>38</v>
+      <c r="D10" s="7" t="s">
+        <v>36</v>
       </c>
       <c r="E10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F10" t="s">
         <v>39</v>
-      </c>
-      <c r="F10" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B11">
         <v>2</v>
@@ -721,18 +781,18 @@
         <v>1.17</v>
       </c>
       <c r="D11" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E11" t="s">
+        <v>43</v>
+      </c>
+      <c r="F11" t="s">
         <v>44</v>
-      </c>
-      <c r="E11" t="s">
-        <v>45</v>
-      </c>
-      <c r="F11" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B12">
         <v>1</v>
@@ -740,19 +800,19 @@
       <c r="C12" s="2">
         <v>1.27</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="7" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" t="s">
         <v>48</v>
-      </c>
-      <c r="E12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F12" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -760,33 +820,132 @@
       <c r="C13" s="2">
         <v>1.37</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="7" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" t="s">
         <v>52</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>15141</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" s="2">
+        <v>4.96</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="E14" t="s">
         <v>54</v>
       </c>
-      <c r="F13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C14" s="2"/>
+      <c r="F14" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C15" s="2"/>
+      <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" s="2">
+        <v>3.97</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15" t="s">
+        <v>58</v>
+      </c>
+      <c r="F15" t="s">
+        <v>59</v>
+      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C16" s="2"/>
+      <c r="A16" t="s">
+        <v>64</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" s="2">
+        <v>1.22</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="E16" t="s">
+        <v>63</v>
+      </c>
+      <c r="F16" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C17" s="2"/>
+      <c r="A17" t="s">
+        <v>65</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" s="2">
+        <v>19.3</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="E17" t="s">
+        <v>67</v>
+      </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C18" s="2"/>
+      <c r="A18" t="s">
+        <v>68</v>
+      </c>
+      <c r="B18">
+        <v>1</v>
+      </c>
+      <c r="C18" s="2">
+        <v>1.29</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" t="s">
+        <v>69</v>
+      </c>
+      <c r="F18" t="s">
+        <v>48</v>
+      </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C19" s="2"/>
+      <c r="A19" t="s">
+        <v>74</v>
+      </c>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" s="2">
+        <v>0.47</v>
+      </c>
+      <c r="D19" t="s">
+        <v>71</v>
+      </c>
+      <c r="E19" t="s">
+        <v>72</v>
+      </c>
+      <c r="F19" t="s">
+        <v>73</v>
+      </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C20" s="2"/>
@@ -3749,6 +3908,15 @@
     <hyperlink ref="D7" r:id="rId5" xr:uid="{C3C00219-F6A4-49A2-ACE4-A106BF51F8FC}"/>
     <hyperlink ref="D9" r:id="rId6" xr:uid="{BB613A42-BF29-46C8-907A-BEAAC1535931}"/>
     <hyperlink ref="D11" r:id="rId7" display="https://www.digikey.com/en/products/detail/omron-electronics-inc-emc-div/B3U-1100P/1534339?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20234014242&amp;gbraid=0AAAAADrbLlis3Cz40t9hjOioxPaFcy7Si&amp;gclid=Cj0KCQjw9ZLSBhCcARIsAEhGKgMMIXBGDglw2WMnyUzLqVsnmpcDYfhjn9ClIkeviY8wOCGYYd3g9hoaAp_GEALw_wcB" xr:uid="{11DBBCC3-C1AB-458D-A13D-AB15568895F1}"/>
+    <hyperlink ref="D14" r:id="rId8" xr:uid="{6A6E6808-941F-4C31-B55C-25EEA0A532B9}"/>
+    <hyperlink ref="D15" r:id="rId9" xr:uid="{A7614A74-8585-4583-88C7-7C64D434FE6B}"/>
+    <hyperlink ref="D12" r:id="rId10" xr:uid="{0DA95EDA-91D1-42C6-97C8-6FB121587AFD}"/>
+    <hyperlink ref="D5" r:id="rId11" xr:uid="{BA27FBC6-665B-44D1-9D26-90D79BF0713C}"/>
+    <hyperlink ref="D18" r:id="rId12" xr:uid="{D5895E37-1669-4BE0-9DCE-10CD65FA4419}"/>
+    <hyperlink ref="D16" r:id="rId13" xr:uid="{F205D0CD-AB7B-445E-B35A-43F47E1629F6}"/>
+    <hyperlink ref="D13" r:id="rId14" xr:uid="{A0292413-CD35-4D7B-A741-27405701ED7D}"/>
+    <hyperlink ref="D10" r:id="rId15" xr:uid="{2E1AE9FB-8DAC-43A4-998B-E8A7954B5508}"/>
+    <hyperlink ref="D17" r:id="rId16" xr:uid="{976EA0AD-2FAA-4CD8-979D-2E724CFC378C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/PhantomBOM.xlsx
+++ b/PhantomBOM.xlsx
@@ -5,22 +5,35 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7bd69513486a8436/Documents/Phantom/Phantom/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pigxt\OneDrive\Documents\Phantom\Phantom\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="135" documentId="8_{C253D126-2466-4473-A8D9-932367B4E877}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E9820A6-E2B7-485A-8FDD-BB43185EF14A}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257D4AD0-D27F-4955-A321-82C4115D3E5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="732" yWindow="732" windowWidth="17280" windowHeight="9960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="113">
   <si>
     <t>Item Name</t>
   </si>
@@ -157,15 +170,6 @@
     <t>SW1,SW2</t>
   </si>
   <si>
-    <t>U.FL-R-SMT-1(80)</t>
-  </si>
-  <si>
-    <t>https://www.digikey.com/en/products/detail/hirose-electric-co-ltd/U-FL-R-SMT-1-80/12143318</t>
-  </si>
-  <si>
-    <t>Antenna Connector</t>
-  </si>
-  <si>
     <t>J4</t>
   </si>
   <si>
@@ -245,6 +249,129 @@
   </si>
   <si>
     <t>B2B-PH-SM4-TB</t>
+  </si>
+  <si>
+    <t>C0603C104K5RACTU</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/kemet/C0603C104K5RACTU/1465594</t>
+  </si>
+  <si>
+    <t>100nF Capacitor</t>
+  </si>
+  <si>
+    <t>C1608X5R1H105K080AB</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/tdk/C1608X5R1H105K080AB/2732903</t>
+  </si>
+  <si>
+    <t>1uF Capacitor</t>
+  </si>
+  <si>
+    <t>C1,C3,C4,C7,C8,C10,C12,C13,C15</t>
+  </si>
+  <si>
+    <t>C5,C9</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/samsung-electro-mechanics/CL21A226KOQNNNE/5961010</t>
+  </si>
+  <si>
+    <t>CL21A226KOQNNNE</t>
+  </si>
+  <si>
+    <t>22uF Capacitor</t>
+  </si>
+  <si>
+    <t>C2</t>
+  </si>
+  <si>
+    <t>CL21A225KOFNNNE</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/samsung-electro-mechanics/CL21A225KOFNNNE/3887439</t>
+  </si>
+  <si>
+    <t>C6,C14</t>
+  </si>
+  <si>
+    <t>CL21A106KOFNNNE</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/samsung-electro-mechanics/CL21A106KOFNNNE/3888551</t>
+  </si>
+  <si>
+    <t>10uF Capcitor</t>
+  </si>
+  <si>
+    <t>2.2uF Capacitor</t>
+  </si>
+  <si>
+    <t>C11</t>
+  </si>
+  <si>
+    <t>CR0603-FX-1002ELF</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/bourns-inc/CR0603-FX-1002ELF/3593188</t>
+  </si>
+  <si>
+    <t>10k Ohm Resistor</t>
+  </si>
+  <si>
+    <t>CR2512-FX-2001ELF</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/bourns-inc/CR2512-FX-2001ELF/4698121?s=N4IgjCBcpgbFoDGUBmBDANgZwKYBoQB7KAbRAHYBmAVjGvgF0CAHAFyhAGVWAnASwB2AcxABfAmACcADkkIQySOmz4ipEAAYQDcSABMG6dXmLluAsUhk9AAgDWAeQAWAWyzaW7SCACqAvqwOKACyOGhYAK48OGIEALR6JlC8EaqWZMY68XLQCsk8qRbqlNq6cRC5ppjmalbgYNKluol1AEo4WHxYrIQ8pUA</t>
+  </si>
+  <si>
+    <t>2k Ohm Resistor</t>
+  </si>
+  <si>
+    <t>R3</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/koa-speer-electronics-inc/RN73H1JTTD2032D25/10682841</t>
+  </si>
+  <si>
+    <t>20k Ohm Resistor</t>
+  </si>
+  <si>
+    <t>R2</t>
+  </si>
+  <si>
+    <t>RN73H1JTTD2032D25</t>
+  </si>
+  <si>
+    <t>CRGH0603F10R</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/te-connectivity-passive-product/CRGH0603F10R/2386211</t>
+  </si>
+  <si>
+    <t>10 Ohm Resistor</t>
+  </si>
+  <si>
+    <t>R12</t>
+  </si>
+  <si>
+    <t>MCT06030Z0000ZP500</t>
+  </si>
+  <si>
+    <t>R17,R18</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/en/products/detail/vishay/MCT06030Z0000ZP500/2607867</t>
+  </si>
+  <si>
+    <t>0 Ohm Resistor</t>
+  </si>
+  <si>
+    <t>R1,R4,R5,R6,R7,R8,R9,R10,11,R13,R14,R15,R16</t>
+  </si>
+  <si>
+    <t>PCB</t>
   </si>
 </sst>
 </file>
@@ -254,7 +381,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -299,6 +426,18 @@
       <color rgb="FF0000FF"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="10"/>
+      <color rgb="FF434343"/>
+      <name val="Arial"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -327,7 +466,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -337,6 +476,9 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -353,10 +495,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -652,7 +790,7 @@
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="B5">
         <v>1</v>
@@ -661,7 +799,7 @@
         <v>0.8</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E5" t="s">
         <v>26</v>
@@ -792,27 +930,19 @@
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>45</v>
+        <v>112</v>
       </c>
       <c r="B12">
         <v>1</v>
       </c>
       <c r="C12" s="2">
-        <v>1.27</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="E12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F12" t="s">
-        <v>48</v>
-      </c>
+        <v>121.62</v>
+      </c>
+      <c r="D12" s="7"/>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="B13">
         <v>1</v>
@@ -821,13 +951,13 @@
         <v>1.37</v>
       </c>
       <c r="D13" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E13" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="F13" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
@@ -841,18 +971,18 @@
         <v>4.96</v>
       </c>
       <c r="D14" s="7" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E14" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="F14" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="B15">
         <v>1</v>
@@ -861,18 +991,18 @@
         <v>3.97</v>
       </c>
       <c r="D15" s="7" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E15" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F15" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="B16">
         <v>1</v>
@@ -881,10 +1011,10 @@
         <v>1.22</v>
       </c>
       <c r="D16" s="7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="E16" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F16" t="s">
         <v>24</v>
@@ -892,7 +1022,7 @@
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="B17">
         <v>1</v>
@@ -901,15 +1031,15 @@
         <v>19.3</v>
       </c>
       <c r="D17" s="7" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E17" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="B18">
         <v>1</v>
@@ -918,18 +1048,18 @@
         <v>1.29</v>
       </c>
       <c r="D18" s="7" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="E18" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F18" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="B19">
         <v>1</v>
@@ -938,55 +1068,223 @@
         <v>0.47</v>
       </c>
       <c r="D19" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E19" t="s">
+        <v>69</v>
+      </c>
+      <c r="F19" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="F19" t="s">
+      <c r="B20" s="1">
+        <v>9</v>
+      </c>
+      <c r="C20" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="D20" s="8" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C20" s="2"/>
+      <c r="E20" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>78</v>
+      </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="B21" s="1">
+        <v>2</v>
+      </c>
+      <c r="C21" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="6" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>81</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="D22" t="s">
+        <v>80</v>
+      </c>
+      <c r="E22" t="s">
+        <v>82</v>
+      </c>
+      <c r="F22" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>84</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+      <c r="C23" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="D23" t="s">
+        <v>85</v>
+      </c>
+      <c r="E23" t="s">
+        <v>90</v>
+      </c>
+      <c r="F23" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>87</v>
+      </c>
+      <c r="B24">
+        <v>1</v>
+      </c>
+      <c r="C24" s="2">
+        <v>0.16</v>
+      </c>
+      <c r="D24" t="s">
+        <v>88</v>
+      </c>
+      <c r="E24" t="s">
+        <v>89</v>
+      </c>
+      <c r="F24" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B25" s="1">
+        <v>13</v>
+      </c>
+      <c r="C25" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="D25" s="8" t="s">
+        <v>93</v>
+      </c>
+      <c r="E25" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="B26" s="9">
+        <v>1</v>
+      </c>
+      <c r="C26" s="5">
+        <v>0.23</v>
+      </c>
+      <c r="D26" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="E26" s="6" t="s">
+        <v>97</v>
+      </c>
+      <c r="F26" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>102</v>
+      </c>
+      <c r="B27" s="11">
+        <v>1</v>
+      </c>
+      <c r="C27" s="2">
+        <v>0.1</v>
+      </c>
+      <c r="D27" t="s">
+        <v>99</v>
+      </c>
+      <c r="E27" t="s">
+        <v>100</v>
+      </c>
+      <c r="F27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>103</v>
+      </c>
+      <c r="B28" s="11">
+        <v>1</v>
+      </c>
+      <c r="C28" s="2">
+        <v>0.12</v>
+      </c>
+      <c r="D28" t="s">
+        <v>104</v>
+      </c>
+      <c r="E28" t="s">
+        <v>105</v>
+      </c>
+      <c r="F28" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>107</v>
+      </c>
+      <c r="B29" s="11">
+        <v>2</v>
+      </c>
+      <c r="C29" s="2">
+        <v>0.19</v>
+      </c>
+      <c r="D29" t="s">
+        <v>109</v>
+      </c>
+      <c r="E29" t="s">
+        <v>110</v>
+      </c>
+      <c r="F29" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B21" s="4">
-        <v>6.7</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="6"/>
-      <c r="E21" s="6"/>
-      <c r="F21" s="6"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C22" s="2"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C23" s="2"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C24" s="2"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C25" s="2"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C26" s="2"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C27" s="2"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C28" s="2"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C29" s="2"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="B30" s="4">
+        <f>SUMPRODUCT(B2:B29, C2:C29)</f>
+        <v>207.26999999999998</v>
+      </c>
       <c r="C30" s="2"/>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -3910,13 +4208,16 @@
     <hyperlink ref="D11" r:id="rId7" display="https://www.digikey.com/en/products/detail/omron-electronics-inc-emc-div/B3U-1100P/1534339?gclsrc=aw.ds&amp;gad_source=1&amp;gad_campaignid=20234014242&amp;gbraid=0AAAAADrbLlis3Cz40t9hjOioxPaFcy7Si&amp;gclid=Cj0KCQjw9ZLSBhCcARIsAEhGKgMMIXBGDglw2WMnyUzLqVsnmpcDYfhjn9ClIkeviY8wOCGYYd3g9hoaAp_GEALw_wcB" xr:uid="{11DBBCC3-C1AB-458D-A13D-AB15568895F1}"/>
     <hyperlink ref="D14" r:id="rId8" xr:uid="{6A6E6808-941F-4C31-B55C-25EEA0A532B9}"/>
     <hyperlink ref="D15" r:id="rId9" xr:uid="{A7614A74-8585-4583-88C7-7C64D434FE6B}"/>
-    <hyperlink ref="D12" r:id="rId10" xr:uid="{0DA95EDA-91D1-42C6-97C8-6FB121587AFD}"/>
-    <hyperlink ref="D5" r:id="rId11" xr:uid="{BA27FBC6-665B-44D1-9D26-90D79BF0713C}"/>
-    <hyperlink ref="D18" r:id="rId12" xr:uid="{D5895E37-1669-4BE0-9DCE-10CD65FA4419}"/>
-    <hyperlink ref="D16" r:id="rId13" xr:uid="{F205D0CD-AB7B-445E-B35A-43F47E1629F6}"/>
-    <hyperlink ref="D13" r:id="rId14" xr:uid="{A0292413-CD35-4D7B-A741-27405701ED7D}"/>
-    <hyperlink ref="D10" r:id="rId15" xr:uid="{2E1AE9FB-8DAC-43A4-998B-E8A7954B5508}"/>
-    <hyperlink ref="D17" r:id="rId16" xr:uid="{976EA0AD-2FAA-4CD8-979D-2E724CFC378C}"/>
+    <hyperlink ref="D5" r:id="rId10" xr:uid="{BA27FBC6-665B-44D1-9D26-90D79BF0713C}"/>
+    <hyperlink ref="D18" r:id="rId11" xr:uid="{D5895E37-1669-4BE0-9DCE-10CD65FA4419}"/>
+    <hyperlink ref="D16" r:id="rId12" xr:uid="{F205D0CD-AB7B-445E-B35A-43F47E1629F6}"/>
+    <hyperlink ref="D13" r:id="rId13" xr:uid="{A0292413-CD35-4D7B-A741-27405701ED7D}"/>
+    <hyperlink ref="D10" r:id="rId14" xr:uid="{2E1AE9FB-8DAC-43A4-998B-E8A7954B5508}"/>
+    <hyperlink ref="D17" r:id="rId15" xr:uid="{976EA0AD-2FAA-4CD8-979D-2E724CFC378C}"/>
+    <hyperlink ref="D20" r:id="rId16" xr:uid="{2ED51F4F-DEA6-455A-8674-43EFE9939E26}"/>
+    <hyperlink ref="D21" r:id="rId17" xr:uid="{E10B70DC-228D-4708-B6B4-4E7C1906453C}"/>
+    <hyperlink ref="D25" r:id="rId18" xr:uid="{1C5CB2EA-C210-4EBF-886F-860711F29F89}"/>
+    <hyperlink ref="D26" r:id="rId19" xr:uid="{89438EAE-D258-4AA1-BFF9-8EC1DCF9BBD2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
